--- a/raw data/Helen_AcclimationData_stickleback_10and1min.xlsx
+++ b/raw data/Helen_AcclimationData_stickleback_10and1min.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10110"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/helen/Desktop/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ljmu-my.sharepoint.com/personal/nspszaji_ljmu_ac_uk/Documents/R &amp; Stats/Acclimation/raw data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C88CDE88-DAAA-344E-AC13-A75D1981632C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="8" documentId="8_{C88CDE88-DAAA-344E-AC13-A75D1981632C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DC191757-104A-4EC6-80F0-86876D07FE7F}"/>
   <bookViews>
-    <workbookView xWindow="380" yWindow="500" windowWidth="28040" windowHeight="16160" xr2:uid="{682BFC1C-55D4-7548-B692-137CFCB24BC9}"/>
+    <workbookView xWindow="37815" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{682BFC1C-55D4-7548-B692-137CFCB24BC9}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -260,12 +260,30 @@
       <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="5">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="0" tint="-0.14999847407452621"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.79998168889431442"/>
+        <bgColor indexed="64"/>
+      </patternFill>
     </fill>
   </fills>
   <borders count="1">
@@ -280,11 +298,20 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="13">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="20" fontId="1" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="2" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" fillId="4" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="4" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -303,9 +330,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -343,7 +370,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -449,7 +476,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -591,7 +618,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -600,15 +627,18 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25D861FB-907E-174D-BB59-2882214F8FF0}">
   <dimension ref="A1:AD97"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="16" x14ac:dyDescent="0.2"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="12" max="12" width="14.83203125" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.83203125" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="12" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="22.5" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.375" customWidth="1"/>
+    <col min="12" max="12" width="12" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.875" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.875" style="6" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="22.5" style="9" bestFit="1" customWidth="1"/>
+    <col min="16" max="16" width="11" style="9"/>
+    <col min="20" max="20" width="11" style="12"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="1" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -643,18 +673,18 @@
         <v>10</v>
       </c>
       <c r="L1" s="1" t="s">
+        <v>62</v>
+      </c>
+      <c r="M1" s="1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" s="4" t="s">
         <v>11</v>
       </c>
-      <c r="M1" s="1" t="s">
-        <v>12</v>
-      </c>
-      <c r="N1" s="1" t="s">
-        <v>62</v>
-      </c>
-      <c r="O1" s="1" t="s">
+      <c r="O1" s="7" t="s">
         <v>63</v>
       </c>
-      <c r="P1" s="1" t="s">
+      <c r="P1" s="7" t="s">
         <v>64</v>
       </c>
       <c r="Q1" s="1" t="s">
@@ -666,7 +696,7 @@
       <c r="S1" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="T1" s="1" t="s">
+      <c r="T1" s="10" t="s">
         <v>16</v>
       </c>
       <c r="U1" s="1" t="s">
@@ -700,7 +730,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="2" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A2" s="2" t="s">
         <v>27</v>
       </c>
@@ -735,18 +765,18 @@
         <v>165</v>
       </c>
       <c r="L2" s="2">
-        <v>600</v>
+        <v>232</v>
       </c>
       <c r="M2" s="2">
         <v>446</v>
       </c>
-      <c r="N2" s="2">
-        <v>232</v>
-      </c>
-      <c r="O2" s="2">
+      <c r="N2" s="5">
+        <v>600</v>
+      </c>
+      <c r="O2" s="8">
         <v>61</v>
       </c>
-      <c r="P2" s="2">
+      <c r="P2" s="8">
         <v>38</v>
       </c>
       <c r="Q2" s="2" t="s">
@@ -758,7 +788,7 @@
       <c r="S2" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="T2" s="2">
+      <c r="T2" s="11">
         <v>73</v>
       </c>
       <c r="U2" s="2">
@@ -792,7 +822,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="3" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A3" s="2" t="s">
         <v>27</v>
       </c>
@@ -827,18 +857,18 @@
         <v>135</v>
       </c>
       <c r="L3" s="2">
-        <v>600</v>
+        <v>15</v>
       </c>
       <c r="M3" s="2">
         <v>295</v>
       </c>
-      <c r="N3" s="2">
-        <v>15</v>
-      </c>
-      <c r="O3" s="2">
+      <c r="N3" s="5">
+        <v>600</v>
+      </c>
+      <c r="O3" s="8">
         <v>53</v>
       </c>
-      <c r="P3" s="2">
+      <c r="P3" s="8">
         <v>29</v>
       </c>
       <c r="Q3" s="2" t="s">
@@ -850,7 +880,7 @@
       <c r="S3" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="T3" s="2">
+      <c r="T3" s="11">
         <v>73</v>
       </c>
       <c r="U3" s="2">
@@ -884,7 +914,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="4" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A4" s="2" t="s">
         <v>27</v>
       </c>
@@ -919,18 +949,18 @@
         <v>36</v>
       </c>
       <c r="L4" s="2">
-        <v>600</v>
+        <v>52</v>
       </c>
       <c r="M4" s="2">
         <v>299</v>
       </c>
-      <c r="N4" s="2">
-        <v>52</v>
-      </c>
-      <c r="O4" s="2">
+      <c r="N4" s="5">
+        <v>600</v>
+      </c>
+      <c r="O4" s="8">
         <v>31</v>
       </c>
-      <c r="P4" s="2">
+      <c r="P4" s="8">
         <v>4</v>
       </c>
       <c r="Q4" s="2" t="s">
@@ -942,7 +972,7 @@
       <c r="S4" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="T4" s="2">
+      <c r="T4" s="11">
         <v>73</v>
       </c>
       <c r="U4" s="2">
@@ -976,7 +1006,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A5" s="2" t="s">
         <v>27</v>
       </c>
@@ -1011,18 +1041,18 @@
         <v>8</v>
       </c>
       <c r="L5" s="2">
-        <v>592</v>
+        <v>396</v>
       </c>
       <c r="M5" s="2">
         <v>414</v>
       </c>
-      <c r="N5" s="2">
-        <v>396</v>
-      </c>
-      <c r="O5" s="2">
+      <c r="N5" s="5">
+        <v>592</v>
+      </c>
+      <c r="O5" s="8">
         <v>24</v>
       </c>
-      <c r="P5" s="2">
+      <c r="P5" s="8">
         <v>58</v>
       </c>
       <c r="Q5" s="2" t="s">
@@ -1034,7 +1064,7 @@
       <c r="S5" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="T5" s="2">
+      <c r="T5" s="11">
         <v>73</v>
       </c>
       <c r="U5" s="2">
@@ -1068,7 +1098,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A6" s="2" t="s">
         <v>27</v>
       </c>
@@ -1103,18 +1133,18 @@
         <v>1</v>
       </c>
       <c r="L6" s="2">
-        <v>600</v>
+        <v>168</v>
       </c>
       <c r="M6" s="2">
         <v>361</v>
       </c>
-      <c r="N6" s="2">
-        <v>168</v>
-      </c>
-      <c r="O6" s="2">
+      <c r="N6" s="5">
+        <v>600</v>
+      </c>
+      <c r="O6" s="8">
         <v>15</v>
       </c>
-      <c r="P6" s="2">
+      <c r="P6" s="8">
         <v>17</v>
       </c>
       <c r="Q6" s="2" t="s">
@@ -1126,7 +1156,7 @@
       <c r="S6" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="T6" s="2">
+      <c r="T6" s="11">
         <v>73</v>
       </c>
       <c r="U6" s="2">
@@ -1160,7 +1190,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A7" s="2" t="s">
         <v>27</v>
       </c>
@@ -1195,18 +1225,18 @@
         <v>126</v>
       </c>
       <c r="L7" s="2">
-        <v>600</v>
+        <v>33</v>
       </c>
       <c r="M7" s="2">
         <v>226</v>
       </c>
-      <c r="N7" s="2">
-        <v>33</v>
-      </c>
-      <c r="O7" s="2">
+      <c r="N7" s="5">
+        <v>600</v>
+      </c>
+      <c r="O7" s="8">
         <v>0</v>
       </c>
-      <c r="P7" s="2">
+      <c r="P7" s="8">
         <v>0</v>
       </c>
       <c r="Q7" s="2" t="s">
@@ -1218,7 +1248,7 @@
       <c r="S7" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="T7" s="2">
+      <c r="T7" s="11">
         <v>73</v>
       </c>
       <c r="U7" s="2">
@@ -1252,7 +1282,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="8" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A8" s="2" t="s">
         <v>27</v>
       </c>
@@ -1287,18 +1317,18 @@
         <v>54</v>
       </c>
       <c r="L8" s="2">
-        <v>592</v>
+        <v>97</v>
       </c>
       <c r="M8" s="2">
         <v>414</v>
       </c>
-      <c r="N8" s="2">
-        <v>97</v>
-      </c>
-      <c r="O8" s="2">
+      <c r="N8" s="5">
+        <v>592</v>
+      </c>
+      <c r="O8" s="8">
         <v>0</v>
       </c>
-      <c r="P8" s="2">
+      <c r="P8" s="8">
         <v>0</v>
       </c>
       <c r="Q8" s="2" t="s">
@@ -1310,7 +1340,7 @@
       <c r="S8" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="T8" s="2">
+      <c r="T8" s="11">
         <v>73</v>
       </c>
       <c r="U8" s="2">
@@ -1344,7 +1374,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="9" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A9" s="2" t="s">
         <v>27</v>
       </c>
@@ -1379,18 +1409,18 @@
         <v>65</v>
       </c>
       <c r="L9" s="2">
-        <v>600</v>
+        <v>144</v>
       </c>
       <c r="M9" s="2">
         <v>463</v>
       </c>
-      <c r="N9" s="2">
-        <v>144</v>
-      </c>
-      <c r="O9" s="2">
+      <c r="N9" s="5">
+        <v>600</v>
+      </c>
+      <c r="O9" s="8">
         <v>9</v>
       </c>
-      <c r="P9" s="2">
+      <c r="P9" s="8">
         <v>60</v>
       </c>
       <c r="Q9" s="2" t="s">
@@ -1402,7 +1432,7 @@
       <c r="S9" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="T9" s="2">
+      <c r="T9" s="11">
         <v>73</v>
       </c>
       <c r="U9" s="2">
@@ -1436,7 +1466,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="10" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A10" s="2" t="s">
         <v>27</v>
       </c>
@@ -1471,18 +1501,18 @@
         <v>80</v>
       </c>
       <c r="L10" s="2">
-        <v>599</v>
+        <v>34</v>
       </c>
       <c r="M10" s="2">
         <v>417</v>
       </c>
-      <c r="N10" s="2">
-        <v>34</v>
-      </c>
-      <c r="O10" s="2">
+      <c r="N10" s="5">
+        <v>599</v>
+      </c>
+      <c r="O10" s="8">
         <v>7</v>
       </c>
-      <c r="P10" s="2">
+      <c r="P10" s="8">
         <v>0</v>
       </c>
       <c r="Q10" s="2" t="s">
@@ -1494,7 +1524,7 @@
       <c r="S10" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="T10" s="2">
+      <c r="T10" s="11">
         <v>73</v>
       </c>
       <c r="U10" s="2">
@@ -1528,7 +1558,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="11" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A11" s="2" t="s">
         <v>27</v>
       </c>
@@ -1563,18 +1593,18 @@
         <v>221</v>
       </c>
       <c r="L11" s="2">
-        <v>600</v>
+        <v>254</v>
       </c>
       <c r="M11" s="2">
         <v>371</v>
       </c>
-      <c r="N11" s="2">
-        <v>254</v>
-      </c>
-      <c r="O11" s="2">
+      <c r="N11" s="5">
+        <v>600</v>
+      </c>
+      <c r="O11" s="8">
         <v>6</v>
       </c>
-      <c r="P11" s="2">
+      <c r="P11" s="8">
         <v>56</v>
       </c>
       <c r="Q11" s="2" t="s">
@@ -1586,7 +1616,7 @@
       <c r="S11" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="T11" s="2">
+      <c r="T11" s="11">
         <v>73</v>
       </c>
       <c r="U11" s="2">
@@ -1620,7 +1650,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="12" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A12" s="2" t="s">
         <v>27</v>
       </c>
@@ -1655,18 +1685,18 @@
         <v>204</v>
       </c>
       <c r="L12" s="2">
-        <v>600</v>
+        <v>39</v>
       </c>
       <c r="M12" s="2">
         <v>285</v>
       </c>
-      <c r="N12" s="2">
-        <v>39</v>
-      </c>
-      <c r="O12" s="2">
+      <c r="N12" s="5">
+        <v>600</v>
+      </c>
+      <c r="O12" s="8">
         <v>0</v>
       </c>
-      <c r="P12" s="2">
+      <c r="P12" s="8">
         <v>0</v>
       </c>
       <c r="Q12" s="2" t="s">
@@ -1678,7 +1708,7 @@
       <c r="S12" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="T12" s="2">
+      <c r="T12" s="11">
         <v>73</v>
       </c>
       <c r="U12" s="2">
@@ -1712,7 +1742,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="13" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A13" s="2" t="s">
         <v>27</v>
       </c>
@@ -1747,18 +1777,18 @@
         <v>231</v>
       </c>
       <c r="L13" s="2">
-        <v>600</v>
+        <v>33</v>
       </c>
       <c r="M13" s="2">
         <v>127</v>
       </c>
-      <c r="N13" s="2">
-        <v>33</v>
-      </c>
-      <c r="O13" s="2">
+      <c r="N13" s="5">
+        <v>600</v>
+      </c>
+      <c r="O13" s="8">
         <v>0</v>
       </c>
-      <c r="P13" s="2">
+      <c r="P13" s="8">
         <v>61</v>
       </c>
       <c r="Q13" s="2" t="s">
@@ -1770,7 +1800,7 @@
       <c r="S13" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="T13" s="2">
+      <c r="T13" s="11">
         <v>73</v>
       </c>
       <c r="U13" s="2">
@@ -1804,7 +1834,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="14" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A14" s="2" t="s">
         <v>27</v>
       </c>
@@ -1839,18 +1869,18 @@
         <v>43</v>
       </c>
       <c r="L14" s="2">
-        <v>600</v>
+        <v>98</v>
       </c>
       <c r="M14" s="2">
         <v>320</v>
       </c>
-      <c r="N14" s="2">
-        <v>98</v>
-      </c>
-      <c r="O14" s="2">
+      <c r="N14" s="5">
+        <v>600</v>
+      </c>
+      <c r="O14" s="8">
         <v>0</v>
       </c>
-      <c r="P14" s="2">
+      <c r="P14" s="8">
         <v>0</v>
       </c>
       <c r="Q14" s="2" t="s">
@@ -1862,7 +1892,7 @@
       <c r="S14" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="T14" s="2">
+      <c r="T14" s="11">
         <v>73</v>
       </c>
       <c r="U14" s="2">
@@ -1896,7 +1926,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A15" s="2" t="s">
         <v>27</v>
       </c>
@@ -1931,18 +1961,18 @@
         <v>148</v>
       </c>
       <c r="L15" s="2">
-        <v>600</v>
+        <v>141</v>
       </c>
       <c r="M15" s="2">
         <v>324</v>
       </c>
-      <c r="N15" s="2">
-        <v>141</v>
-      </c>
-      <c r="O15" s="2">
+      <c r="N15" s="5">
+        <v>600</v>
+      </c>
+      <c r="O15" s="8">
         <v>0</v>
       </c>
-      <c r="P15" s="2">
+      <c r="P15" s="8">
         <v>0</v>
       </c>
       <c r="Q15" s="2" t="s">
@@ -1954,7 +1984,7 @@
       <c r="S15" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="T15" s="2">
+      <c r="T15" s="11">
         <v>73</v>
       </c>
       <c r="U15" s="2">
@@ -1988,7 +2018,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="16" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A16" s="2" t="s">
         <v>27</v>
       </c>
@@ -2023,18 +2053,18 @@
         <v>131</v>
       </c>
       <c r="L16" s="2">
-        <v>600</v>
+        <v>87</v>
       </c>
       <c r="M16" s="2">
         <v>350</v>
       </c>
-      <c r="N16" s="2">
-        <v>87</v>
-      </c>
-      <c r="O16" s="2">
+      <c r="N16" s="5">
+        <v>600</v>
+      </c>
+      <c r="O16" s="8">
         <v>0</v>
       </c>
-      <c r="P16" s="2">
+      <c r="P16" s="8">
         <v>0</v>
       </c>
       <c r="Q16" s="2" t="s">
@@ -2046,7 +2076,7 @@
       <c r="S16" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="T16" s="2">
+      <c r="T16" s="11">
         <v>73</v>
       </c>
       <c r="U16" s="2">
@@ -2080,7 +2110,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="17" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="17" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A17" s="2" t="s">
         <v>27</v>
       </c>
@@ -2115,18 +2145,18 @@
         <v>133</v>
       </c>
       <c r="L17" s="2">
-        <v>600</v>
+        <v>269</v>
       </c>
       <c r="M17" s="2">
         <v>499</v>
       </c>
-      <c r="N17" s="2">
-        <v>269</v>
-      </c>
-      <c r="O17" s="2">
+      <c r="N17" s="5">
+        <v>600</v>
+      </c>
+      <c r="O17" s="8">
         <v>1</v>
       </c>
-      <c r="P17" s="2">
+      <c r="P17" s="8">
         <v>0</v>
       </c>
       <c r="Q17" s="2" t="s">
@@ -2138,7 +2168,7 @@
       <c r="S17" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="T17" s="2">
+      <c r="T17" s="11">
         <v>73</v>
       </c>
       <c r="U17" s="2">
@@ -2172,7 +2202,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="18" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="18" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A18" s="2" t="s">
         <v>27</v>
       </c>
@@ -2207,18 +2237,18 @@
         <v>60</v>
       </c>
       <c r="L18" s="2">
-        <v>600</v>
+        <v>199</v>
       </c>
       <c r="M18" s="2">
         <v>538</v>
       </c>
-      <c r="N18" s="2">
-        <v>199</v>
-      </c>
-      <c r="O18" s="2">
+      <c r="N18" s="5">
+        <v>600</v>
+      </c>
+      <c r="O18" s="8">
         <v>23</v>
       </c>
-      <c r="P18" s="2">
+      <c r="P18" s="8">
         <v>3</v>
       </c>
       <c r="Q18" s="2" t="s">
@@ -2230,7 +2260,7 @@
       <c r="S18" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="T18" s="2">
+      <c r="T18" s="11">
         <v>73</v>
       </c>
       <c r="U18" s="2">
@@ -2264,7 +2294,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="19" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="19" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A19" s="2" t="s">
         <v>27</v>
       </c>
@@ -2299,18 +2329,18 @@
         <v>75</v>
       </c>
       <c r="L19" s="2">
-        <v>600</v>
+        <v>128</v>
       </c>
       <c r="M19" s="2">
         <v>523</v>
       </c>
-      <c r="N19" s="2">
-        <v>128</v>
-      </c>
-      <c r="O19" s="2">
+      <c r="N19" s="5">
+        <v>600</v>
+      </c>
+      <c r="O19" s="8">
         <v>39</v>
       </c>
-      <c r="P19" s="2">
+      <c r="P19" s="8">
         <v>0</v>
       </c>
       <c r="Q19" s="2" t="s">
@@ -2322,7 +2352,7 @@
       <c r="S19" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="T19" s="2">
+      <c r="T19" s="11">
         <v>73</v>
       </c>
       <c r="U19" s="2">
@@ -2356,7 +2386,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="20" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="20" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A20" s="2" t="s">
         <v>27</v>
       </c>
@@ -2391,18 +2421,18 @@
         <v>4</v>
       </c>
       <c r="L20" s="2">
-        <v>600</v>
+        <v>250</v>
       </c>
       <c r="M20" s="2">
         <v>418</v>
       </c>
-      <c r="N20" s="2">
-        <v>250</v>
-      </c>
-      <c r="O20" s="2">
+      <c r="N20" s="5">
+        <v>600</v>
+      </c>
+      <c r="O20" s="8">
         <v>15</v>
       </c>
-      <c r="P20" s="2">
+      <c r="P20" s="8">
         <v>0</v>
       </c>
       <c r="Q20" s="2" t="s">
@@ -2414,7 +2444,7 @@
       <c r="S20" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="T20" s="2">
+      <c r="T20" s="11">
         <v>73</v>
       </c>
       <c r="U20" s="2">
@@ -2448,7 +2478,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="21" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="21" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A21" s="2" t="s">
         <v>27</v>
       </c>
@@ -2483,18 +2513,18 @@
         <v>1</v>
       </c>
       <c r="L21" s="2">
-        <v>596</v>
+        <v>122</v>
       </c>
       <c r="M21" s="2">
         <v>443</v>
       </c>
-      <c r="N21" s="2">
-        <v>122</v>
-      </c>
-      <c r="O21" s="2">
+      <c r="N21" s="5">
+        <v>596</v>
+      </c>
+      <c r="O21" s="8">
         <v>20</v>
       </c>
-      <c r="P21" s="2">
+      <c r="P21" s="8">
         <v>0</v>
       </c>
       <c r="Q21" s="2" t="s">
@@ -2506,7 +2536,7 @@
       <c r="S21" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="T21" s="2">
+      <c r="T21" s="11">
         <v>73</v>
       </c>
       <c r="U21" s="2">
@@ -2540,7 +2570,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="22" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="22" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A22" s="2" t="s">
         <v>27</v>
       </c>
@@ -2575,18 +2605,18 @@
         <v>161</v>
       </c>
       <c r="L22" s="2">
-        <v>600</v>
+        <v>185</v>
       </c>
       <c r="M22" s="2">
         <v>391</v>
       </c>
-      <c r="N22" s="2">
-        <v>185</v>
-      </c>
-      <c r="O22" s="2">
+      <c r="N22" s="5">
+        <v>600</v>
+      </c>
+      <c r="O22" s="8">
         <v>56</v>
       </c>
-      <c r="P22" s="2">
+      <c r="P22" s="8">
         <v>34</v>
       </c>
       <c r="Q22" s="2" t="s">
@@ -2598,7 +2628,7 @@
       <c r="S22" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="T22" s="2">
+      <c r="T22" s="11">
         <v>73</v>
       </c>
       <c r="U22" s="2">
@@ -2632,7 +2662,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="23" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="23" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A23" s="2" t="s">
         <v>27</v>
       </c>
@@ -2667,18 +2697,18 @@
         <v>4</v>
       </c>
       <c r="L23" s="2">
-        <v>600</v>
+        <v>31</v>
       </c>
       <c r="M23" s="2">
         <v>439</v>
       </c>
-      <c r="N23" s="2">
-        <v>31</v>
-      </c>
-      <c r="O23" s="2">
+      <c r="N23" s="5">
+        <v>600</v>
+      </c>
+      <c r="O23" s="8">
         <v>7</v>
       </c>
-      <c r="P23" s="2">
+      <c r="P23" s="8">
         <v>0</v>
       </c>
       <c r="Q23" s="2" t="s">
@@ -2690,7 +2720,7 @@
       <c r="S23" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="T23" s="2">
+      <c r="T23" s="11">
         <v>73</v>
       </c>
       <c r="U23" s="2">
@@ -2724,7 +2754,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="24" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="24" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A24" s="2" t="s">
         <v>27</v>
       </c>
@@ -2759,18 +2789,18 @@
         <v>11</v>
       </c>
       <c r="L24" s="2">
-        <v>600</v>
+        <v>68</v>
       </c>
       <c r="M24" s="2">
         <v>418</v>
       </c>
-      <c r="N24" s="2">
-        <v>68</v>
-      </c>
-      <c r="O24" s="2">
+      <c r="N24" s="5">
+        <v>600</v>
+      </c>
+      <c r="O24" s="8">
         <v>11</v>
       </c>
-      <c r="P24" s="2">
+      <c r="P24" s="8">
         <v>0</v>
       </c>
       <c r="Q24" s="2" t="s">
@@ -2782,7 +2812,7 @@
       <c r="S24" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="T24" s="2">
+      <c r="T24" s="11">
         <v>73</v>
       </c>
       <c r="U24" s="2">
@@ -2816,7 +2846,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="25" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="25" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A25" s="2" t="s">
         <v>27</v>
       </c>
@@ -2851,18 +2881,18 @@
         <v>12</v>
       </c>
       <c r="L25" s="2">
-        <v>600</v>
+        <v>22</v>
       </c>
       <c r="M25" s="2">
         <v>378</v>
       </c>
-      <c r="N25" s="2">
-        <v>22</v>
-      </c>
-      <c r="O25" s="2">
+      <c r="N25" s="5">
+        <v>600</v>
+      </c>
+      <c r="O25" s="8">
         <v>19</v>
       </c>
-      <c r="P25" s="2">
+      <c r="P25" s="8">
         <v>0</v>
       </c>
       <c r="Q25" s="2" t="s">
@@ -2874,7 +2904,7 @@
       <c r="S25" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="T25" s="2">
+      <c r="T25" s="11">
         <v>73</v>
       </c>
       <c r="U25" s="2">
@@ -2908,7 +2938,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="26" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="26" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A26" s="2" t="s">
         <v>27</v>
       </c>
@@ -2943,18 +2973,18 @@
         <v>36</v>
       </c>
       <c r="L26" s="2">
-        <v>600</v>
+        <v>2</v>
       </c>
       <c r="M26" s="2">
         <v>399</v>
       </c>
-      <c r="N26" s="2">
-        <v>2</v>
-      </c>
-      <c r="O26" s="2">
+      <c r="N26" s="5">
+        <v>600</v>
+      </c>
+      <c r="O26" s="8">
         <v>4</v>
       </c>
-      <c r="P26" s="2">
+      <c r="P26" s="8">
         <v>0</v>
       </c>
       <c r="Q26" s="2" t="s">
@@ -2966,7 +2996,7 @@
       <c r="S26" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="T26" s="2">
+      <c r="T26" s="11">
         <v>73</v>
       </c>
       <c r="U26" s="2">
@@ -3000,7 +3030,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="27" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="27" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A27" s="2" t="s">
         <v>27</v>
       </c>
@@ -3035,18 +3065,18 @@
         <v>35</v>
       </c>
       <c r="L27" s="2">
-        <v>597</v>
+        <v>67</v>
       </c>
       <c r="M27" s="2">
         <v>381</v>
       </c>
-      <c r="N27" s="2">
-        <v>67</v>
-      </c>
-      <c r="O27" s="2">
+      <c r="N27" s="5">
+        <v>597</v>
+      </c>
+      <c r="O27" s="8">
         <v>5</v>
       </c>
-      <c r="P27" s="2">
+      <c r="P27" s="8">
         <v>0</v>
       </c>
       <c r="Q27" s="2" t="s">
@@ -3058,7 +3088,7 @@
       <c r="S27" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="T27" s="2">
+      <c r="T27" s="11">
         <v>73</v>
       </c>
       <c r="U27" s="2">
@@ -3092,7 +3122,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="28" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="28" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A28" s="2" t="s">
         <v>27</v>
       </c>
@@ -3127,18 +3157,18 @@
         <v>23</v>
       </c>
       <c r="L28" s="2">
-        <v>592</v>
+        <v>85</v>
       </c>
       <c r="M28" s="2">
         <v>378</v>
       </c>
-      <c r="N28" s="2">
-        <v>85</v>
-      </c>
-      <c r="O28" s="2">
+      <c r="N28" s="5">
+        <v>592</v>
+      </c>
+      <c r="O28" s="8">
         <v>1</v>
       </c>
-      <c r="P28" s="2">
+      <c r="P28" s="8">
         <v>0</v>
       </c>
       <c r="Q28" s="2" t="s">
@@ -3150,7 +3180,7 @@
       <c r="S28" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="T28" s="2">
+      <c r="T28" s="11">
         <v>73</v>
       </c>
       <c r="U28" s="2">
@@ -3184,7 +3214,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="29" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="29" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A29" s="2" t="s">
         <v>27</v>
       </c>
@@ -3219,18 +3249,18 @@
         <v>1</v>
       </c>
       <c r="L29" s="2">
-        <v>600</v>
+        <v>122</v>
       </c>
       <c r="M29" s="2">
         <v>505</v>
       </c>
-      <c r="N29" s="2">
-        <v>122</v>
-      </c>
-      <c r="O29" s="2">
+      <c r="N29" s="5">
+        <v>600</v>
+      </c>
+      <c r="O29" s="8">
         <v>54</v>
       </c>
-      <c r="P29" s="2">
+      <c r="P29" s="8">
         <v>0</v>
       </c>
       <c r="Q29" s="2" t="s">
@@ -3242,7 +3272,7 @@
       <c r="S29" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="T29" s="2">
+      <c r="T29" s="11">
         <v>73</v>
       </c>
       <c r="U29" s="2">
@@ -3276,7 +3306,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="30" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="30" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A30" s="2" t="s">
         <v>27</v>
       </c>
@@ -3311,18 +3341,18 @@
         <v>323</v>
       </c>
       <c r="L30" s="2">
-        <v>600</v>
+        <v>122</v>
       </c>
       <c r="M30" s="2">
         <v>282</v>
       </c>
-      <c r="N30" s="2">
-        <v>122</v>
-      </c>
-      <c r="O30" s="2">
-        <v>28</v>
-      </c>
-      <c r="P30" s="2">
+      <c r="N30" s="5">
+        <v>600</v>
+      </c>
+      <c r="O30" s="8">
+        <v>28</v>
+      </c>
+      <c r="P30" s="8">
         <v>0</v>
       </c>
       <c r="Q30" s="2" t="s">
@@ -3334,7 +3364,7 @@
       <c r="S30" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="T30" s="2">
+      <c r="T30" s="11">
         <v>73</v>
       </c>
       <c r="U30" s="2">
@@ -3368,7 +3398,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="31" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="31" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A31" s="2" t="s">
         <v>27</v>
       </c>
@@ -3403,18 +3433,18 @@
         <v>178</v>
       </c>
       <c r="L31" s="2">
-        <v>600</v>
+        <v>264</v>
       </c>
       <c r="M31" s="2">
         <v>509</v>
       </c>
-      <c r="N31" s="2">
-        <v>264</v>
-      </c>
-      <c r="O31" s="2">
+      <c r="N31" s="5">
+        <v>600</v>
+      </c>
+      <c r="O31" s="8">
         <v>48</v>
       </c>
-      <c r="P31" s="2">
+      <c r="P31" s="8">
         <v>29</v>
       </c>
       <c r="Q31" s="2" t="s">
@@ -3426,7 +3456,7 @@
       <c r="S31" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="T31" s="2">
+      <c r="T31" s="11">
         <v>73</v>
       </c>
       <c r="U31" s="2">
@@ -3460,7 +3490,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="32" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="32" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A32" s="2" t="s">
         <v>27</v>
       </c>
@@ -3495,18 +3525,18 @@
         <v>2</v>
       </c>
       <c r="L32" s="2">
-        <v>600</v>
+        <v>140</v>
       </c>
       <c r="M32" s="2">
         <v>503</v>
       </c>
-      <c r="N32" s="2">
-        <v>140</v>
-      </c>
-      <c r="O32" s="2">
+      <c r="N32" s="5">
+        <v>600</v>
+      </c>
+      <c r="O32" s="8">
         <v>4</v>
       </c>
-      <c r="P32" s="2">
+      <c r="P32" s="8">
         <v>0</v>
       </c>
       <c r="Q32" s="2" t="s">
@@ -3518,7 +3548,7 @@
       <c r="S32" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="T32" s="2">
+      <c r="T32" s="11">
         <v>73</v>
       </c>
       <c r="U32" s="2">
@@ -3552,7 +3582,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="33" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="33" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A33" s="2" t="s">
         <v>27</v>
       </c>
@@ -3587,18 +3617,18 @@
         <v>1</v>
       </c>
       <c r="L33" s="2">
-        <v>600</v>
+        <v>322</v>
       </c>
       <c r="M33" s="2">
         <v>492</v>
       </c>
-      <c r="N33" s="2">
-        <v>322</v>
-      </c>
-      <c r="O33" s="2">
+      <c r="N33" s="5">
+        <v>600</v>
+      </c>
+      <c r="O33" s="8">
         <v>11</v>
       </c>
-      <c r="P33" s="2">
+      <c r="P33" s="8">
         <v>50</v>
       </c>
       <c r="Q33" s="2" t="s">
@@ -3610,7 +3640,7 @@
       <c r="S33" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="T33" s="2">
+      <c r="T33" s="11">
         <v>73</v>
       </c>
       <c r="U33" s="2">
@@ -3644,7 +3674,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="34" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="34" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A34" s="2" t="s">
         <v>27</v>
       </c>
@@ -3679,18 +3709,18 @@
         <v>3</v>
       </c>
       <c r="L34" s="2">
-        <v>600</v>
+        <v>48</v>
       </c>
       <c r="M34" s="2">
         <v>441</v>
       </c>
-      <c r="N34" s="2">
-        <v>48</v>
-      </c>
-      <c r="O34" s="2">
+      <c r="N34" s="5">
+        <v>600</v>
+      </c>
+      <c r="O34" s="8">
         <v>39</v>
       </c>
-      <c r="P34" s="2">
+      <c r="P34" s="8">
         <v>0</v>
       </c>
       <c r="Q34" s="2" t="s">
@@ -3702,7 +3732,7 @@
       <c r="S34" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="T34" s="2">
+      <c r="T34" s="11">
         <v>73</v>
       </c>
       <c r="U34" s="2">
@@ -3736,7 +3766,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="35" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="35" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A35" s="2" t="s">
         <v>27</v>
       </c>
@@ -3771,20 +3801,20 @@
         <v>1</v>
       </c>
       <c r="L35" s="2">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="M35" s="2">
         <v>363</v>
       </c>
-      <c r="N35" s="2">
+      <c r="N35" s="5">
+        <v>600</v>
+      </c>
+      <c r="O35" s="8">
         <v>0</v>
       </c>
-      <c r="O35" s="2">
+      <c r="P35" s="8">
         <v>0</v>
       </c>
-      <c r="P35" s="2">
-        <v>0</v>
-      </c>
       <c r="Q35" s="2" t="s">
         <v>34</v>
       </c>
@@ -3794,7 +3824,7 @@
       <c r="S35" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="T35" s="2">
+      <c r="T35" s="11">
         <v>73</v>
       </c>
       <c r="U35" s="2">
@@ -3828,7 +3858,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="36" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="36" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A36" s="2" t="s">
         <v>27</v>
       </c>
@@ -3863,18 +3893,18 @@
         <v>26</v>
       </c>
       <c r="L36" s="2">
-        <v>600</v>
+        <v>95</v>
       </c>
       <c r="M36" s="2">
         <v>447</v>
       </c>
-      <c r="N36" s="2">
-        <v>95</v>
-      </c>
-      <c r="O36" s="2">
+      <c r="N36" s="5">
+        <v>600</v>
+      </c>
+      <c r="O36" s="8">
         <v>0</v>
       </c>
-      <c r="P36" s="2">
+      <c r="P36" s="8">
         <v>0</v>
       </c>
       <c r="Q36" s="2" t="s">
@@ -3886,7 +3916,7 @@
       <c r="S36" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="T36" s="2">
+      <c r="T36" s="11">
         <v>73</v>
       </c>
       <c r="U36" s="2">
@@ -3920,7 +3950,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="37" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="37" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A37" s="2" t="s">
         <v>27</v>
       </c>
@@ -3955,20 +3985,20 @@
         <v>55</v>
       </c>
       <c r="L37" s="2">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="M37" s="2">
         <v>334</v>
       </c>
-      <c r="N37" s="2">
+      <c r="N37" s="5">
+        <v>600</v>
+      </c>
+      <c r="O37" s="8">
         <v>0</v>
       </c>
-      <c r="O37" s="2">
+      <c r="P37" s="8">
         <v>0</v>
       </c>
-      <c r="P37" s="2">
-        <v>0</v>
-      </c>
       <c r="Q37" s="2" t="s">
         <v>34</v>
       </c>
@@ -3978,7 +4008,7 @@
       <c r="S37" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="T37" s="2">
+      <c r="T37" s="11">
         <v>73</v>
       </c>
       <c r="U37" s="2">
@@ -4012,7 +4042,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="38" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="38" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A38" s="2" t="s">
         <v>27</v>
       </c>
@@ -4047,18 +4077,18 @@
         <v>260</v>
       </c>
       <c r="L38" s="2">
-        <v>590</v>
+        <v>91</v>
       </c>
       <c r="M38" s="2">
         <v>456</v>
       </c>
-      <c r="N38" s="2">
-        <v>91</v>
-      </c>
-      <c r="O38" s="2">
+      <c r="N38" s="5">
+        <v>590</v>
+      </c>
+      <c r="O38" s="8">
         <v>57</v>
       </c>
-      <c r="P38" s="2">
+      <c r="P38" s="8">
         <v>46</v>
       </c>
       <c r="Q38" s="2" t="s">
@@ -4070,7 +4100,7 @@
       <c r="S38" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="T38" s="2">
+      <c r="T38" s="11">
         <v>73</v>
       </c>
       <c r="U38" s="2">
@@ -4104,7 +4134,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="39" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="39" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A39" s="2" t="s">
         <v>27</v>
       </c>
@@ -4139,18 +4169,18 @@
         <v>198</v>
       </c>
       <c r="L39" s="2">
-        <v>600</v>
+        <v>4</v>
       </c>
       <c r="M39" s="2">
         <v>286</v>
       </c>
-      <c r="N39" s="2">
-        <v>4</v>
-      </c>
-      <c r="O39" s="2">
+      <c r="N39" s="5">
+        <v>600</v>
+      </c>
+      <c r="O39" s="8">
         <v>42</v>
       </c>
-      <c r="P39" s="2">
+      <c r="P39" s="8">
         <v>19</v>
       </c>
       <c r="Q39" s="2" t="s">
@@ -4162,7 +4192,7 @@
       <c r="S39" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="T39" s="2">
+      <c r="T39" s="11">
         <v>73</v>
       </c>
       <c r="U39" s="2">
@@ -4196,7 +4226,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="40" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="40" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A40" s="2" t="s">
         <v>27</v>
       </c>
@@ -4231,20 +4261,20 @@
         <v>341</v>
       </c>
       <c r="L40" s="2">
-        <v>600</v>
+        <v>39</v>
       </c>
       <c r="M40" s="2">
         <v>281</v>
       </c>
-      <c r="N40" s="2">
+      <c r="N40" s="5">
+        <v>600</v>
+      </c>
+      <c r="O40" s="8">
+        <v>56</v>
+      </c>
+      <c r="P40" s="8">
         <v>39</v>
       </c>
-      <c r="O40" s="2">
-        <v>56</v>
-      </c>
-      <c r="P40" s="2">
-        <v>39</v>
-      </c>
       <c r="Q40" s="2" t="s">
         <v>34</v>
       </c>
@@ -4254,7 +4284,7 @@
       <c r="S40" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="T40" s="2">
+      <c r="T40" s="11">
         <v>73</v>
       </c>
       <c r="U40" s="2">
@@ -4288,7 +4318,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="41" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="41" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A41" s="2" t="s">
         <v>27</v>
       </c>
@@ -4323,18 +4353,18 @@
         <v>107</v>
       </c>
       <c r="L41" s="2">
-        <v>600</v>
+        <v>46</v>
       </c>
       <c r="M41" s="2">
         <v>356</v>
       </c>
-      <c r="N41" s="2">
-        <v>46</v>
-      </c>
-      <c r="O41" s="2">
+      <c r="N41" s="5">
+        <v>600</v>
+      </c>
+      <c r="O41" s="8">
         <v>11</v>
       </c>
-      <c r="P41" s="2">
+      <c r="P41" s="8">
         <v>0</v>
       </c>
       <c r="Q41" s="2" t="s">
@@ -4346,7 +4376,7 @@
       <c r="S41" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="T41" s="2">
+      <c r="T41" s="11">
         <v>73</v>
       </c>
       <c r="U41" s="2">
@@ -4380,7 +4410,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="42" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="42" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A42" s="2" t="s">
         <v>27</v>
       </c>
@@ -4415,18 +4445,18 @@
         <v>1</v>
       </c>
       <c r="L42" s="2">
-        <v>600</v>
+        <v>3</v>
       </c>
       <c r="M42" s="2">
         <v>306</v>
       </c>
-      <c r="N42" s="2">
-        <v>3</v>
-      </c>
-      <c r="O42" s="2">
+      <c r="N42" s="5">
+        <v>600</v>
+      </c>
+      <c r="O42" s="8">
         <v>4</v>
       </c>
-      <c r="P42" s="2">
+      <c r="P42" s="8">
         <v>0</v>
       </c>
       <c r="Q42" s="2" t="s">
@@ -4438,7 +4468,7 @@
       <c r="S42" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="T42" s="2">
+      <c r="T42" s="11">
         <v>73</v>
       </c>
       <c r="U42" s="2">
@@ -4472,7 +4502,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="43" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="43" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A43" s="2" t="s">
         <v>27</v>
       </c>
@@ -4507,18 +4537,18 @@
         <v>2</v>
       </c>
       <c r="L43" s="2">
-        <v>600</v>
+        <v>3</v>
       </c>
       <c r="M43" s="2">
         <v>411</v>
       </c>
-      <c r="N43" s="2">
-        <v>3</v>
-      </c>
-      <c r="O43" s="2">
+      <c r="N43" s="5">
+        <v>600</v>
+      </c>
+      <c r="O43" s="8">
         <v>13</v>
       </c>
-      <c r="P43" s="2">
+      <c r="P43" s="8">
         <v>0</v>
       </c>
       <c r="Q43" s="2" t="s">
@@ -4530,7 +4560,7 @@
       <c r="S43" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="T43" s="2">
+      <c r="T43" s="11">
         <v>73</v>
       </c>
       <c r="U43" s="2">
@@ -4564,7 +4594,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="44" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="44" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A44" s="2" t="s">
         <v>27</v>
       </c>
@@ -4599,18 +4629,18 @@
         <v>70</v>
       </c>
       <c r="L44" s="2">
-        <v>600</v>
+        <v>339</v>
       </c>
       <c r="M44" s="2">
         <v>297</v>
       </c>
-      <c r="N44" s="2">
-        <v>339</v>
-      </c>
-      <c r="O44" s="2">
+      <c r="N44" s="5">
+        <v>600</v>
+      </c>
+      <c r="O44" s="8">
         <v>52</v>
       </c>
-      <c r="P44" s="2">
+      <c r="P44" s="8">
         <v>37</v>
       </c>
       <c r="Q44" s="2" t="s">
@@ -4622,7 +4652,7 @@
       <c r="S44" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="T44" s="2">
+      <c r="T44" s="11">
         <v>73</v>
       </c>
       <c r="U44" s="2">
@@ -4656,7 +4686,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="45" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="45" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A45" s="2" t="s">
         <v>27</v>
       </c>
@@ -4691,18 +4721,18 @@
         <v>18</v>
       </c>
       <c r="L45" s="2">
-        <v>588</v>
+        <v>255</v>
       </c>
       <c r="M45" s="2">
         <v>402</v>
       </c>
-      <c r="N45" s="2">
-        <v>255</v>
-      </c>
-      <c r="O45" s="2">
+      <c r="N45" s="5">
+        <v>588</v>
+      </c>
+      <c r="O45" s="8">
         <v>2</v>
       </c>
-      <c r="P45" s="2">
+      <c r="P45" s="8">
         <v>0</v>
       </c>
       <c r="Q45" s="2" t="s">
@@ -4714,7 +4744,7 @@
       <c r="S45" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="T45" s="2">
+      <c r="T45" s="11">
         <v>73</v>
       </c>
       <c r="U45" s="2">
@@ -4748,7 +4778,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="46" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="46" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A46" s="2" t="s">
         <v>27</v>
       </c>
@@ -4783,18 +4813,18 @@
         <v>24</v>
       </c>
       <c r="L46" s="2">
-        <v>587</v>
+        <v>131</v>
       </c>
       <c r="M46" s="2">
         <v>346</v>
       </c>
-      <c r="N46" s="2">
-        <v>131</v>
-      </c>
-      <c r="O46" s="2">
+      <c r="N46" s="5">
+        <v>587</v>
+      </c>
+      <c r="O46" s="8">
         <v>1</v>
       </c>
-      <c r="P46" s="2">
+      <c r="P46" s="8">
         <v>0</v>
       </c>
       <c r="Q46" s="2" t="s">
@@ -4806,7 +4836,7 @@
       <c r="S46" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="T46" s="2">
+      <c r="T46" s="11">
         <v>73</v>
       </c>
       <c r="U46" s="2">
@@ -4840,7 +4870,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="47" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="47" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A47" s="2" t="s">
         <v>27</v>
       </c>
@@ -4875,18 +4905,18 @@
         <v>214</v>
       </c>
       <c r="L47" s="2">
-        <v>600</v>
+        <v>196</v>
       </c>
       <c r="M47" s="2">
         <v>349</v>
       </c>
-      <c r="N47" s="2">
-        <v>196</v>
-      </c>
-      <c r="O47" s="2">
+      <c r="N47" s="5">
+        <v>600</v>
+      </c>
+      <c r="O47" s="8">
         <v>40</v>
       </c>
-      <c r="P47" s="2">
+      <c r="P47" s="8">
         <v>58</v>
       </c>
       <c r="Q47" s="2" t="s">
@@ -4898,7 +4928,7 @@
       <c r="S47" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="T47" s="2">
+      <c r="T47" s="11">
         <v>73</v>
       </c>
       <c r="U47" s="2">
@@ -4932,7 +4962,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="48" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="48" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A48" s="2" t="s">
         <v>27</v>
       </c>
@@ -4967,18 +4997,18 @@
         <v>155</v>
       </c>
       <c r="L48" s="2">
-        <v>600</v>
+        <v>227</v>
       </c>
       <c r="M48" s="2">
         <v>286</v>
       </c>
-      <c r="N48" s="2">
-        <v>227</v>
-      </c>
-      <c r="O48" s="2">
+      <c r="N48" s="5">
+        <v>600</v>
+      </c>
+      <c r="O48" s="8">
         <v>23</v>
       </c>
-      <c r="P48" s="2">
+      <c r="P48" s="8">
         <v>43</v>
       </c>
       <c r="Q48" s="2" t="s">
@@ -4990,7 +5020,7 @@
       <c r="S48" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="T48" s="2">
+      <c r="T48" s="11">
         <v>73</v>
       </c>
       <c r="U48" s="2">
@@ -5024,7 +5054,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="49" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="49" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A49" s="2" t="s">
         <v>27</v>
       </c>
@@ -5059,18 +5089,18 @@
         <v>35</v>
       </c>
       <c r="L49" s="2">
-        <v>600</v>
+        <v>329</v>
       </c>
       <c r="M49" s="2">
         <v>280</v>
       </c>
-      <c r="N49" s="2">
-        <v>329</v>
-      </c>
-      <c r="O49" s="2">
+      <c r="N49" s="5">
+        <v>600</v>
+      </c>
+      <c r="O49" s="8">
         <v>23</v>
       </c>
-      <c r="P49" s="2">
+      <c r="P49" s="8">
         <v>46</v>
       </c>
       <c r="Q49" s="2" t="s">
@@ -5082,7 +5112,7 @@
       <c r="S49" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="T49" s="2">
+      <c r="T49" s="11">
         <v>73</v>
       </c>
       <c r="U49" s="2">
@@ -5116,7 +5146,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="50" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="50" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A50" s="2" t="s">
         <v>27</v>
       </c>
@@ -5151,18 +5181,18 @@
         <v>142</v>
       </c>
       <c r="L50" s="2">
-        <v>600</v>
+        <v>41</v>
       </c>
       <c r="M50" s="2">
         <v>267</v>
       </c>
-      <c r="N50" s="2">
-        <v>41</v>
-      </c>
-      <c r="O50" s="2">
+      <c r="N50" s="5">
+        <v>600</v>
+      </c>
+      <c r="O50" s="8">
         <v>49</v>
       </c>
-      <c r="P50" s="2">
+      <c r="P50" s="8">
         <v>36</v>
       </c>
       <c r="Q50" s="2" t="s">
@@ -5174,7 +5204,7 @@
       <c r="S50" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="T50" s="2">
+      <c r="T50" s="11">
         <v>73</v>
       </c>
       <c r="U50" s="2">
@@ -5208,7 +5238,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="51" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="51" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A51" s="2" t="s">
         <v>27</v>
       </c>
@@ -5243,18 +5273,18 @@
         <v>216</v>
       </c>
       <c r="L51" s="2">
-        <v>600</v>
+        <v>16</v>
       </c>
       <c r="M51" s="2">
         <v>253</v>
       </c>
-      <c r="N51" s="2">
-        <v>16</v>
-      </c>
-      <c r="O51" s="2">
+      <c r="N51" s="5">
+        <v>600</v>
+      </c>
+      <c r="O51" s="8">
         <v>0</v>
       </c>
-      <c r="P51" s="2">
+      <c r="P51" s="8">
         <v>0</v>
       </c>
       <c r="Q51" s="2" t="s">
@@ -5266,7 +5296,7 @@
       <c r="S51" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="T51" s="2">
+      <c r="T51" s="11">
         <v>73</v>
       </c>
       <c r="U51" s="2">
@@ -5300,7 +5330,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="52" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="52" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A52" s="2" t="s">
         <v>27</v>
       </c>
@@ -5335,18 +5365,18 @@
         <v>131</v>
       </c>
       <c r="L52" s="2">
-        <v>600</v>
+        <v>106</v>
       </c>
       <c r="M52" s="2">
         <v>353</v>
       </c>
-      <c r="N52" s="2">
-        <v>106</v>
-      </c>
-      <c r="O52" s="2">
+      <c r="N52" s="5">
+        <v>600</v>
+      </c>
+      <c r="O52" s="8">
         <v>0</v>
       </c>
-      <c r="P52" s="2">
+      <c r="P52" s="8">
         <v>0</v>
       </c>
       <c r="Q52" s="2" t="s">
@@ -5358,7 +5388,7 @@
       <c r="S52" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="T52" s="2">
+      <c r="T52" s="11">
         <v>73</v>
       </c>
       <c r="U52" s="2">
@@ -5392,7 +5422,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="53" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="53" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A53" s="2" t="s">
         <v>27</v>
       </c>
@@ -5427,18 +5457,18 @@
         <v>5</v>
       </c>
       <c r="L53" s="2">
-        <v>600</v>
+        <v>270</v>
       </c>
       <c r="M53" s="2">
         <v>497</v>
       </c>
-      <c r="N53" s="2">
-        <v>270</v>
-      </c>
-      <c r="O53" s="2">
+      <c r="N53" s="5">
+        <v>600</v>
+      </c>
+      <c r="O53" s="8">
         <v>1</v>
       </c>
-      <c r="P53" s="2">
+      <c r="P53" s="8">
         <v>0</v>
       </c>
       <c r="Q53" s="2" t="s">
@@ -5450,7 +5480,7 @@
       <c r="S53" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="T53" s="2">
+      <c r="T53" s="11">
         <v>73</v>
       </c>
       <c r="U53" s="2">
@@ -5484,7 +5514,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="54" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="54" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A54" s="2" t="s">
         <v>27</v>
       </c>
@@ -5519,18 +5549,18 @@
         <v>31</v>
       </c>
       <c r="L54" s="2">
-        <v>600</v>
+        <v>135</v>
       </c>
       <c r="M54" s="2">
         <v>374</v>
       </c>
-      <c r="N54" s="2">
-        <v>135</v>
-      </c>
-      <c r="O54" s="2">
+      <c r="N54" s="5">
+        <v>600</v>
+      </c>
+      <c r="O54" s="8">
         <v>0</v>
       </c>
-      <c r="P54" s="2">
+      <c r="P54" s="8">
         <v>0</v>
       </c>
       <c r="Q54" s="2" t="s">
@@ -5542,7 +5572,7 @@
       <c r="S54" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="T54" s="2">
+      <c r="T54" s="11">
         <v>73</v>
       </c>
       <c r="U54" s="2">
@@ -5576,7 +5606,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="55" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="55" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A55" s="2" t="s">
         <v>27</v>
       </c>
@@ -5611,18 +5641,18 @@
         <v>1</v>
       </c>
       <c r="L55" s="2">
-        <v>600</v>
+        <v>296</v>
       </c>
       <c r="M55" s="2">
         <v>514</v>
       </c>
-      <c r="N55" s="2">
-        <v>296</v>
-      </c>
-      <c r="O55" s="2">
+      <c r="N55" s="5">
+        <v>600</v>
+      </c>
+      <c r="O55" s="8">
         <v>0</v>
       </c>
-      <c r="P55" s="2">
+      <c r="P55" s="8">
         <v>0</v>
       </c>
       <c r="Q55" s="2" t="s">
@@ -5634,7 +5664,7 @@
       <c r="S55" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="T55" s="2">
+      <c r="T55" s="11">
         <v>73</v>
       </c>
       <c r="U55" s="2">
@@ -5668,7 +5698,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="56" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="56" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A56" s="2" t="s">
         <v>27</v>
       </c>
@@ -5703,18 +5733,18 @@
         <v>208</v>
       </c>
       <c r="L56" s="2">
-        <v>587</v>
+        <v>115</v>
       </c>
       <c r="M56" s="2">
         <v>416</v>
       </c>
-      <c r="N56" s="2">
-        <v>115</v>
-      </c>
-      <c r="O56" s="2">
+      <c r="N56" s="5">
+        <v>587</v>
+      </c>
+      <c r="O56" s="8">
         <v>55</v>
       </c>
-      <c r="P56" s="2">
+      <c r="P56" s="8">
         <v>35</v>
       </c>
       <c r="Q56" s="2" t="s">
@@ -5726,7 +5756,7 @@
       <c r="S56" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="T56" s="2">
+      <c r="T56" s="11">
         <v>73</v>
       </c>
       <c r="U56" s="2">
@@ -5760,7 +5790,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="57" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="57" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A57" s="2" t="s">
         <v>27</v>
       </c>
@@ -5795,20 +5825,20 @@
         <v>588</v>
       </c>
       <c r="L57" s="2">
-        <v>600</v>
+        <v>0</v>
       </c>
       <c r="M57" s="2">
         <v>97</v>
       </c>
-      <c r="N57" s="2">
+      <c r="N57" s="5">
+        <v>600</v>
+      </c>
+      <c r="O57" s="8">
+        <v>22</v>
+      </c>
+      <c r="P57" s="8">
         <v>0</v>
       </c>
-      <c r="O57" s="2">
-        <v>22</v>
-      </c>
-      <c r="P57" s="2">
-        <v>0</v>
-      </c>
       <c r="Q57" s="2" t="s">
         <v>34</v>
       </c>
@@ -5818,7 +5848,7 @@
       <c r="S57" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="T57" s="2">
+      <c r="T57" s="11">
         <v>73</v>
       </c>
       <c r="U57" s="2">
@@ -5852,7 +5882,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="58" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="58" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A58" s="2" t="s">
         <v>27</v>
       </c>
@@ -5887,18 +5917,18 @@
         <v>191</v>
       </c>
       <c r="L58" s="2">
-        <v>600</v>
+        <v>114</v>
       </c>
       <c r="M58" s="2">
         <v>439</v>
       </c>
-      <c r="N58" s="2">
-        <v>114</v>
-      </c>
-      <c r="O58" s="2">
+      <c r="N58" s="5">
+        <v>600</v>
+      </c>
+      <c r="O58" s="8">
         <v>51</v>
       </c>
-      <c r="P58" s="2">
+      <c r="P58" s="8">
         <v>40</v>
       </c>
       <c r="Q58" s="2" t="s">
@@ -5910,7 +5940,7 @@
       <c r="S58" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="T58" s="2">
+      <c r="T58" s="11">
         <v>73</v>
       </c>
       <c r="U58" s="2">
@@ -5944,7 +5974,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="59" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="59" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A59" s="2" t="s">
         <v>27</v>
       </c>
@@ -5979,18 +6009,18 @@
         <v>54</v>
       </c>
       <c r="L59" s="2">
-        <v>600</v>
+        <v>69</v>
       </c>
       <c r="M59" s="2">
         <v>472</v>
       </c>
-      <c r="N59" s="2">
-        <v>69</v>
-      </c>
-      <c r="O59" s="2">
+      <c r="N59" s="5">
+        <v>600</v>
+      </c>
+      <c r="O59" s="8">
         <v>43</v>
       </c>
-      <c r="P59" s="2">
+      <c r="P59" s="8">
         <v>0</v>
       </c>
       <c r="Q59" s="2" t="s">
@@ -6002,7 +6032,7 @@
       <c r="S59" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="T59" s="2">
+      <c r="T59" s="11">
         <v>73</v>
       </c>
       <c r="U59" s="2">
@@ -6036,7 +6066,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="60" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="60" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A60" s="2" t="s">
         <v>27</v>
       </c>
@@ -6071,18 +6101,18 @@
         <v>11</v>
       </c>
       <c r="L60" s="2">
-        <v>600</v>
+        <v>13</v>
       </c>
       <c r="M60" s="2">
         <v>404</v>
       </c>
-      <c r="N60" s="2">
-        <v>13</v>
-      </c>
-      <c r="O60" s="2">
+      <c r="N60" s="5">
+        <v>600</v>
+      </c>
+      <c r="O60" s="8">
         <v>23</v>
       </c>
-      <c r="P60" s="2">
+      <c r="P60" s="8">
         <v>0</v>
       </c>
       <c r="Q60" s="2" t="s">
@@ -6094,7 +6124,7 @@
       <c r="S60" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="T60" s="2">
+      <c r="T60" s="11">
         <v>73</v>
       </c>
       <c r="U60" s="2">
@@ -6128,7 +6158,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="61" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="61" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A61" s="2" t="s">
         <v>27</v>
       </c>
@@ -6163,18 +6193,18 @@
         <v>1</v>
       </c>
       <c r="L61" s="2">
-        <v>600</v>
+        <v>185</v>
       </c>
       <c r="M61" s="2">
         <v>423</v>
       </c>
-      <c r="N61" s="2">
-        <v>185</v>
-      </c>
-      <c r="O61" s="2">
+      <c r="N61" s="5">
+        <v>600</v>
+      </c>
+      <c r="O61" s="8">
         <v>44</v>
       </c>
-      <c r="P61" s="2">
+      <c r="P61" s="8">
         <v>10</v>
       </c>
       <c r="Q61" s="2" t="s">
@@ -6186,7 +6216,7 @@
       <c r="S61" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="T61" s="2">
+      <c r="T61" s="11">
         <v>73</v>
       </c>
       <c r="U61" s="2">
@@ -6220,7 +6250,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="62" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="62" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A62" s="2" t="s">
         <v>27</v>
       </c>
@@ -6255,18 +6285,18 @@
         <v>27</v>
       </c>
       <c r="L62" s="2">
-        <v>585</v>
+        <v>15</v>
       </c>
       <c r="M62" s="2">
         <v>518</v>
       </c>
-      <c r="N62" s="2">
-        <v>15</v>
-      </c>
-      <c r="O62" s="2">
+      <c r="N62" s="5">
+        <v>585</v>
+      </c>
+      <c r="O62" s="8">
         <v>7</v>
       </c>
-      <c r="P62" s="2">
+      <c r="P62" s="8">
         <v>1</v>
       </c>
       <c r="Q62" s="2" t="s">
@@ -6278,7 +6308,7 @@
       <c r="S62" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="T62" s="2">
+      <c r="T62" s="11">
         <v>73</v>
       </c>
       <c r="U62" s="2">
@@ -6312,7 +6342,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="63" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="63" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A63" s="2" t="s">
         <v>27</v>
       </c>
@@ -6347,18 +6377,18 @@
         <v>5</v>
       </c>
       <c r="L63" s="2">
-        <v>590</v>
+        <v>40</v>
       </c>
       <c r="M63" s="2">
         <v>466</v>
       </c>
-      <c r="N63" s="2">
-        <v>40</v>
-      </c>
-      <c r="O63" s="2">
+      <c r="N63" s="5">
+        <v>590</v>
+      </c>
+      <c r="O63" s="8">
         <v>17</v>
       </c>
-      <c r="P63" s="2">
+      <c r="P63" s="8">
         <v>0</v>
       </c>
       <c r="Q63" s="2" t="s">
@@ -6370,7 +6400,7 @@
       <c r="S63" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="T63" s="2">
+      <c r="T63" s="11">
         <v>73</v>
       </c>
       <c r="U63" s="2">
@@ -6404,7 +6434,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="64" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="64" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A64" s="2" t="s">
         <v>27</v>
       </c>
@@ -6439,18 +6469,18 @@
         <v>7</v>
       </c>
       <c r="L64" s="2">
-        <v>591</v>
+        <v>15</v>
       </c>
       <c r="M64" s="2">
         <v>495</v>
       </c>
-      <c r="N64" s="2">
-        <v>15</v>
-      </c>
-      <c r="O64" s="2">
+      <c r="N64" s="5">
+        <v>591</v>
+      </c>
+      <c r="O64" s="8">
         <v>19</v>
       </c>
-      <c r="P64" s="2">
+      <c r="P64" s="8">
         <v>0</v>
       </c>
       <c r="Q64" s="2" t="s">
@@ -6462,7 +6492,7 @@
       <c r="S64" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="T64" s="2">
+      <c r="T64" s="11">
         <v>73</v>
       </c>
       <c r="U64" s="2">
@@ -6496,7 +6526,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="65" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="65" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A65" s="2" t="s">
         <v>27</v>
       </c>
@@ -6531,18 +6561,18 @@
         <v>1</v>
       </c>
       <c r="L65" s="2">
-        <v>600</v>
+        <v>265</v>
       </c>
       <c r="M65" s="2">
         <v>501</v>
       </c>
-      <c r="N65" s="2">
-        <v>265</v>
-      </c>
-      <c r="O65" s="2">
+      <c r="N65" s="5">
+        <v>600</v>
+      </c>
+      <c r="O65" s="8">
         <v>50</v>
       </c>
-      <c r="P65" s="2">
+      <c r="P65" s="8">
         <v>57</v>
       </c>
       <c r="Q65" s="2" t="s">
@@ -6554,7 +6584,7 @@
       <c r="S65" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="T65" s="2">
+      <c r="T65" s="11">
         <v>73</v>
       </c>
       <c r="U65" s="2">
@@ -6588,7 +6618,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="66" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="66" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A66" s="2" t="s">
         <v>27</v>
       </c>
@@ -6623,18 +6653,18 @@
         <v>147</v>
       </c>
       <c r="L66" s="2">
-        <v>600</v>
+        <v>141</v>
       </c>
       <c r="M66" s="2">
         <v>357</v>
       </c>
-      <c r="N66" s="2">
-        <v>141</v>
-      </c>
-      <c r="O66" s="2">
+      <c r="N66" s="5">
+        <v>600</v>
+      </c>
+      <c r="O66" s="8">
         <v>42</v>
       </c>
-      <c r="P66" s="2">
+      <c r="P66" s="8">
         <v>34</v>
       </c>
       <c r="Q66" s="2" t="s">
@@ -6646,7 +6676,7 @@
       <c r="S66" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="T66" s="2">
+      <c r="T66" s="11">
         <v>73</v>
       </c>
       <c r="U66" s="2">
@@ -6680,7 +6710,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="67" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="67" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A67" s="2" t="s">
         <v>27</v>
       </c>
@@ -6715,18 +6745,18 @@
         <v>29</v>
       </c>
       <c r="L67" s="2">
-        <v>600</v>
+        <v>167</v>
       </c>
       <c r="M67" s="2">
         <v>353</v>
       </c>
-      <c r="N67" s="2">
-        <v>167</v>
-      </c>
-      <c r="O67" s="2">
-        <v>33</v>
-      </c>
-      <c r="P67" s="2">
+      <c r="N67" s="5">
+        <v>600</v>
+      </c>
+      <c r="O67" s="8">
+        <v>33</v>
+      </c>
+      <c r="P67" s="8">
         <v>22</v>
       </c>
       <c r="Q67" s="2" t="s">
@@ -6738,7 +6768,7 @@
       <c r="S67" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="T67" s="2">
+      <c r="T67" s="11">
         <v>73</v>
       </c>
       <c r="U67" s="2">
@@ -6772,7 +6802,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="68" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="68" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A68" s="2" t="s">
         <v>27</v>
       </c>
@@ -6807,18 +6837,18 @@
         <v>16</v>
       </c>
       <c r="L68" s="2">
-        <v>600</v>
+        <v>383</v>
       </c>
       <c r="M68" s="2">
         <v>467</v>
       </c>
-      <c r="N68" s="2">
-        <v>383</v>
-      </c>
-      <c r="O68" s="2">
+      <c r="N68" s="5">
+        <v>600</v>
+      </c>
+      <c r="O68" s="8">
         <v>0</v>
       </c>
-      <c r="P68" s="2">
+      <c r="P68" s="8">
         <v>61</v>
       </c>
       <c r="Q68" s="2" t="s">
@@ -6830,7 +6860,7 @@
       <c r="S68" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="T68" s="2">
+      <c r="T68" s="11">
         <v>73</v>
       </c>
       <c r="U68" s="2">
@@ -6864,7 +6894,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="69" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="69" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A69" s="2" t="s">
         <v>27</v>
       </c>
@@ -6899,18 +6929,18 @@
         <v>4</v>
       </c>
       <c r="L69" s="2">
-        <v>600</v>
+        <v>115</v>
       </c>
       <c r="M69" s="2">
         <v>222</v>
       </c>
-      <c r="N69" s="2">
-        <v>115</v>
-      </c>
-      <c r="O69" s="2">
+      <c r="N69" s="5">
+        <v>600</v>
+      </c>
+      <c r="O69" s="8">
         <v>0</v>
       </c>
-      <c r="P69" s="2">
+      <c r="P69" s="8">
         <v>0</v>
       </c>
       <c r="Q69" s="2" t="s">
@@ -6922,7 +6952,7 @@
       <c r="S69" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="T69" s="2">
+      <c r="T69" s="11">
         <v>73</v>
       </c>
       <c r="U69" s="2">
@@ -6956,7 +6986,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="70" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="70" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A70" s="2" t="s">
         <v>27</v>
       </c>
@@ -6991,18 +7021,18 @@
         <v>1</v>
       </c>
       <c r="L70" s="2">
-        <v>600</v>
+        <v>17</v>
       </c>
       <c r="M70" s="2">
         <v>324</v>
       </c>
-      <c r="N70" s="2">
-        <v>17</v>
-      </c>
-      <c r="O70" s="2">
+      <c r="N70" s="5">
+        <v>600</v>
+      </c>
+      <c r="O70" s="8">
         <v>8</v>
       </c>
-      <c r="P70" s="2">
+      <c r="P70" s="8">
         <v>0</v>
       </c>
       <c r="Q70" s="2" t="s">
@@ -7014,7 +7044,7 @@
       <c r="S70" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="T70" s="2">
+      <c r="T70" s="11">
         <v>73</v>
       </c>
       <c r="U70" s="2">
@@ -7048,7 +7078,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="71" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="71" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A71" s="2" t="s">
         <v>27</v>
       </c>
@@ -7083,18 +7113,18 @@
         <v>105</v>
       </c>
       <c r="L71" s="2">
-        <v>600</v>
+        <v>164</v>
       </c>
       <c r="M71" s="2">
         <v>330</v>
       </c>
-      <c r="N71" s="2">
-        <v>164</v>
-      </c>
-      <c r="O71" s="2">
+      <c r="N71" s="5">
+        <v>600</v>
+      </c>
+      <c r="O71" s="8">
         <v>4</v>
       </c>
-      <c r="P71" s="2">
+      <c r="P71" s="8">
         <v>0</v>
       </c>
       <c r="Q71" s="2" t="s">
@@ -7106,7 +7136,7 @@
       <c r="S71" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="T71" s="2">
+      <c r="T71" s="11">
         <v>73</v>
       </c>
       <c r="U71" s="2">
@@ -7140,7 +7170,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="72" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="72" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A72" s="2" t="s">
         <v>27</v>
       </c>
@@ -7175,18 +7205,18 @@
         <v>40</v>
       </c>
       <c r="L72" s="2">
-        <v>600</v>
+        <v>212</v>
       </c>
       <c r="M72" s="2">
         <v>367</v>
       </c>
-      <c r="N72" s="2">
-        <v>212</v>
-      </c>
-      <c r="O72" s="2">
+      <c r="N72" s="5">
+        <v>600</v>
+      </c>
+      <c r="O72" s="8">
         <v>0</v>
       </c>
-      <c r="P72" s="2">
+      <c r="P72" s="8">
         <v>0</v>
       </c>
       <c r="Q72" s="2" t="s">
@@ -7198,7 +7228,7 @@
       <c r="S72" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="T72" s="2">
+      <c r="T72" s="11">
         <v>73</v>
       </c>
       <c r="U72" s="2">
@@ -7232,7 +7262,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="73" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="73" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A73" s="2" t="s">
         <v>27</v>
       </c>
@@ -7267,18 +7297,18 @@
         <v>1</v>
       </c>
       <c r="L73" s="2">
-        <v>600</v>
+        <v>73</v>
       </c>
       <c r="M73" s="2">
         <v>287</v>
       </c>
-      <c r="N73" s="2">
-        <v>73</v>
-      </c>
-      <c r="O73" s="2">
+      <c r="N73" s="5">
+        <v>600</v>
+      </c>
+      <c r="O73" s="8">
         <v>0</v>
       </c>
-      <c r="P73" s="2">
+      <c r="P73" s="8">
         <v>0</v>
       </c>
       <c r="Q73" s="2" t="s">
@@ -7290,7 +7320,7 @@
       <c r="S73" s="2" t="s">
         <v>34</v>
       </c>
-      <c r="T73" s="2">
+      <c r="T73" s="11">
         <v>73</v>
       </c>
       <c r="U73" s="2">
@@ -7324,7 +7354,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="74" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="74" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A74" s="2" t="s">
         <v>27</v>
       </c>
@@ -7360,9 +7390,9 @@
       </c>
       <c r="L74" s="2"/>
       <c r="M74" s="2"/>
-      <c r="N74" s="2"/>
-      <c r="O74" s="2"/>
-      <c r="P74" s="2"/>
+      <c r="N74" s="5"/>
+      <c r="O74" s="8"/>
+      <c r="P74" s="8"/>
       <c r="Q74" s="2">
         <v>10</v>
       </c>
@@ -7372,7 +7402,7 @@
       <c r="S74" s="2">
         <v>156</v>
       </c>
-      <c r="T74" s="2">
+      <c r="T74" s="11">
         <v>73</v>
       </c>
       <c r="U74" s="2">
@@ -7406,7 +7436,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="75" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="75" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A75" s="2" t="s">
         <v>27</v>
       </c>
@@ -7442,9 +7472,9 @@
       </c>
       <c r="L75" s="2"/>
       <c r="M75" s="2"/>
-      <c r="N75" s="2"/>
-      <c r="O75" s="2"/>
-      <c r="P75" s="2"/>
+      <c r="N75" s="5"/>
+      <c r="O75" s="8"/>
+      <c r="P75" s="8"/>
       <c r="Q75" s="2">
         <v>10</v>
       </c>
@@ -7452,7 +7482,7 @@
         <v>103</v>
       </c>
       <c r="S75" s="2"/>
-      <c r="T75" s="2">
+      <c r="T75" s="11">
         <v>73</v>
       </c>
       <c r="U75" s="2">
@@ -7486,7 +7516,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="76" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="76" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A76" s="2" t="s">
         <v>27</v>
       </c>
@@ -7522,9 +7552,9 @@
       </c>
       <c r="L76" s="2"/>
       <c r="M76" s="2"/>
-      <c r="N76" s="2"/>
-      <c r="O76" s="2"/>
-      <c r="P76" s="2"/>
+      <c r="N76" s="5"/>
+      <c r="O76" s="8"/>
+      <c r="P76" s="8"/>
       <c r="Q76" s="2">
         <v>10</v>
       </c>
@@ -7534,7 +7564,7 @@
       <c r="S76" s="2">
         <v>167</v>
       </c>
-      <c r="T76" s="2">
+      <c r="T76" s="11">
         <v>73</v>
       </c>
       <c r="U76" s="2">
@@ -7568,7 +7598,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="77" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="77" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A77" s="2" t="s">
         <v>27</v>
       </c>
@@ -7604,9 +7634,9 @@
       </c>
       <c r="L77" s="2"/>
       <c r="M77" s="2"/>
-      <c r="N77" s="2"/>
-      <c r="O77" s="2"/>
-      <c r="P77" s="2"/>
+      <c r="N77" s="5"/>
+      <c r="O77" s="8"/>
+      <c r="P77" s="8"/>
       <c r="Q77" s="2">
         <v>10</v>
       </c>
@@ -7616,7 +7646,7 @@
       <c r="S77" s="2">
         <v>290</v>
       </c>
-      <c r="T77" s="2">
+      <c r="T77" s="11">
         <v>73</v>
       </c>
       <c r="U77" s="2">
@@ -7650,7 +7680,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="78" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="78" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A78" s="2" t="s">
         <v>27</v>
       </c>
@@ -7686,9 +7716,9 @@
       </c>
       <c r="L78" s="2"/>
       <c r="M78" s="2"/>
-      <c r="N78" s="2"/>
-      <c r="O78" s="2"/>
-      <c r="P78" s="2"/>
+      <c r="N78" s="5"/>
+      <c r="O78" s="8"/>
+      <c r="P78" s="8"/>
       <c r="Q78" s="2">
         <v>10</v>
       </c>
@@ -7698,7 +7728,7 @@
       <c r="S78" s="2">
         <v>122</v>
       </c>
-      <c r="T78" s="2">
+      <c r="T78" s="11">
         <v>73</v>
       </c>
       <c r="U78" s="2">
@@ -7732,7 +7762,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="79" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="79" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A79" s="2" t="s">
         <v>27</v>
       </c>
@@ -7768,9 +7798,9 @@
       </c>
       <c r="L79" s="2"/>
       <c r="M79" s="2"/>
-      <c r="N79" s="2"/>
-      <c r="O79" s="2"/>
-      <c r="P79" s="2"/>
+      <c r="N79" s="5"/>
+      <c r="O79" s="8"/>
+      <c r="P79" s="8"/>
       <c r="Q79" s="2">
         <v>10</v>
       </c>
@@ -7778,7 +7808,7 @@
         <v>144</v>
       </c>
       <c r="S79" s="2"/>
-      <c r="T79" s="2">
+      <c r="T79" s="11">
         <v>73</v>
       </c>
       <c r="U79" s="2">
@@ -7812,7 +7842,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="80" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="80" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A80" s="2" t="s">
         <v>27</v>
       </c>
@@ -7848,9 +7878,9 @@
       </c>
       <c r="L80" s="2"/>
       <c r="M80" s="2"/>
-      <c r="N80" s="2"/>
-      <c r="O80" s="2"/>
-      <c r="P80" s="2"/>
+      <c r="N80" s="5"/>
+      <c r="O80" s="8"/>
+      <c r="P80" s="8"/>
       <c r="Q80" s="2">
         <v>10</v>
       </c>
@@ -7860,7 +7890,7 @@
       <c r="S80" s="2">
         <v>10</v>
       </c>
-      <c r="T80" s="2">
+      <c r="T80" s="11">
         <v>73</v>
       </c>
       <c r="U80" s="2">
@@ -7894,7 +7924,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="81" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="81" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A81" s="2" t="s">
         <v>27</v>
       </c>
@@ -7930,9 +7960,9 @@
       </c>
       <c r="L81" s="2"/>
       <c r="M81" s="2"/>
-      <c r="N81" s="2"/>
-      <c r="O81" s="2"/>
-      <c r="P81" s="2"/>
+      <c r="N81" s="5"/>
+      <c r="O81" s="8"/>
+      <c r="P81" s="8"/>
       <c r="Q81" s="2">
         <v>10</v>
       </c>
@@ -7942,7 +7972,7 @@
       <c r="S81" s="2">
         <v>33</v>
       </c>
-      <c r="T81" s="2">
+      <c r="T81" s="11">
         <v>73</v>
       </c>
       <c r="U81" s="2">
@@ -7976,7 +8006,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="82" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="82" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A82" s="2" t="s">
         <v>27</v>
       </c>
@@ -8012,9 +8042,9 @@
       </c>
       <c r="L82" s="2"/>
       <c r="M82" s="2"/>
-      <c r="N82" s="2"/>
-      <c r="O82" s="2"/>
-      <c r="P82" s="2"/>
+      <c r="N82" s="5"/>
+      <c r="O82" s="8"/>
+      <c r="P82" s="8"/>
       <c r="Q82" s="2">
         <v>10</v>
       </c>
@@ -8024,7 +8054,7 @@
       <c r="S82" s="2">
         <v>76</v>
       </c>
-      <c r="T82" s="2">
+      <c r="T82" s="11">
         <v>73</v>
       </c>
       <c r="U82" s="2">
@@ -8058,7 +8088,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="83" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="83" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A83" s="2" t="s">
         <v>27</v>
       </c>
@@ -8094,9 +8124,9 @@
       </c>
       <c r="L83" s="2"/>
       <c r="M83" s="2"/>
-      <c r="N83" s="2"/>
-      <c r="O83" s="2"/>
-      <c r="P83" s="2"/>
+      <c r="N83" s="5"/>
+      <c r="O83" s="8"/>
+      <c r="P83" s="8"/>
       <c r="Q83" s="2">
         <v>10</v>
       </c>
@@ -8106,7 +8136,7 @@
       <c r="S83" s="2">
         <v>8</v>
       </c>
-      <c r="T83" s="2">
+      <c r="T83" s="11">
         <v>73</v>
       </c>
       <c r="U83" s="2">
@@ -8140,7 +8170,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="84" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="84" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A84" s="2" t="s">
         <v>27</v>
       </c>
@@ -8176,9 +8206,9 @@
       </c>
       <c r="L84" s="2"/>
       <c r="M84" s="2"/>
-      <c r="N84" s="2"/>
-      <c r="O84" s="2"/>
-      <c r="P84" s="2"/>
+      <c r="N84" s="5"/>
+      <c r="O84" s="8"/>
+      <c r="P84" s="8"/>
       <c r="Q84" s="2">
         <v>10</v>
       </c>
@@ -8188,7 +8218,7 @@
       <c r="S84" s="2">
         <v>33</v>
       </c>
-      <c r="T84" s="2">
+      <c r="T84" s="11">
         <v>73</v>
       </c>
       <c r="U84" s="2">
@@ -8222,7 +8252,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="85" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="85" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A85" s="2" t="s">
         <v>27</v>
       </c>
@@ -8258,9 +8288,9 @@
       </c>
       <c r="L85" s="2"/>
       <c r="M85" s="2"/>
-      <c r="N85" s="2"/>
-      <c r="O85" s="2"/>
-      <c r="P85" s="2"/>
+      <c r="N85" s="5"/>
+      <c r="O85" s="8"/>
+      <c r="P85" s="8"/>
       <c r="Q85" s="2">
         <v>10</v>
       </c>
@@ -8270,7 +8300,7 @@
       <c r="S85" s="2">
         <v>114</v>
       </c>
-      <c r="T85" s="2">
+      <c r="T85" s="11">
         <v>73</v>
       </c>
       <c r="U85" s="2">
@@ -8304,7 +8334,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="86" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="86" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A86" s="2" t="s">
         <v>27</v>
       </c>
@@ -8340,9 +8370,9 @@
       </c>
       <c r="L86" s="2"/>
       <c r="M86" s="2"/>
-      <c r="N86" s="2"/>
-      <c r="O86" s="2"/>
-      <c r="P86" s="2"/>
+      <c r="N86" s="5"/>
+      <c r="O86" s="8"/>
+      <c r="P86" s="8"/>
       <c r="Q86" s="2">
         <v>10</v>
       </c>
@@ -8350,7 +8380,7 @@
         <v>1</v>
       </c>
       <c r="S86" s="2"/>
-      <c r="T86" s="2">
+      <c r="T86" s="11">
         <v>73</v>
       </c>
       <c r="U86" s="2">
@@ -8384,7 +8414,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="87" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="87" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A87" s="2" t="s">
         <v>27</v>
       </c>
@@ -8420,9 +8450,9 @@
       </c>
       <c r="L87" s="2"/>
       <c r="M87" s="2"/>
-      <c r="N87" s="2"/>
-      <c r="O87" s="2"/>
-      <c r="P87" s="2"/>
+      <c r="N87" s="5"/>
+      <c r="O87" s="8"/>
+      <c r="P87" s="8"/>
       <c r="Q87" s="2">
         <v>10</v>
       </c>
@@ -8432,7 +8462,7 @@
       <c r="S87" s="2">
         <v>125</v>
       </c>
-      <c r="T87" s="2">
+      <c r="T87" s="11">
         <v>73</v>
       </c>
       <c r="U87" s="2">
@@ -8466,7 +8496,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="88" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="88" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A88" s="2" t="s">
         <v>27</v>
       </c>
@@ -8502,9 +8532,9 @@
       </c>
       <c r="L88" s="2"/>
       <c r="M88" s="2"/>
-      <c r="N88" s="2"/>
-      <c r="O88" s="2"/>
-      <c r="P88" s="2"/>
+      <c r="N88" s="5"/>
+      <c r="O88" s="8"/>
+      <c r="P88" s="8"/>
       <c r="Q88" s="2">
         <v>10</v>
       </c>
@@ -8514,7 +8544,7 @@
       <c r="S88" s="2">
         <v>125</v>
       </c>
-      <c r="T88" s="2">
+      <c r="T88" s="11">
         <v>73</v>
       </c>
       <c r="U88" s="2">
@@ -8548,7 +8578,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="89" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="89" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A89" s="2" t="s">
         <v>27</v>
       </c>
@@ -8584,9 +8614,9 @@
       </c>
       <c r="L89" s="2"/>
       <c r="M89" s="2"/>
-      <c r="N89" s="2"/>
-      <c r="O89" s="2"/>
-      <c r="P89" s="2"/>
+      <c r="N89" s="5"/>
+      <c r="O89" s="8"/>
+      <c r="P89" s="8"/>
       <c r="Q89" s="2">
         <v>10</v>
       </c>
@@ -8596,7 +8626,7 @@
       <c r="S89" s="2">
         <v>112</v>
       </c>
-      <c r="T89" s="2">
+      <c r="T89" s="11">
         <v>73</v>
       </c>
       <c r="U89" s="2">
@@ -8630,7 +8660,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="90" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="90" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A90" s="2" t="s">
         <v>27</v>
       </c>
@@ -8666,9 +8696,9 @@
       </c>
       <c r="L90" s="2"/>
       <c r="M90" s="2"/>
-      <c r="N90" s="2"/>
-      <c r="O90" s="2"/>
-      <c r="P90" s="2"/>
+      <c r="N90" s="5"/>
+      <c r="O90" s="8"/>
+      <c r="P90" s="8"/>
       <c r="Q90" s="2">
         <v>10</v>
       </c>
@@ -8678,7 +8708,7 @@
       <c r="S90" s="2">
         <v>210</v>
       </c>
-      <c r="T90" s="2">
+      <c r="T90" s="11">
         <v>73</v>
       </c>
       <c r="U90" s="2">
@@ -8712,7 +8742,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="91" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="91" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A91" s="2" t="s">
         <v>27</v>
       </c>
@@ -8748,9 +8778,9 @@
       </c>
       <c r="L91" s="2"/>
       <c r="M91" s="2"/>
-      <c r="N91" s="2"/>
-      <c r="O91" s="2"/>
-      <c r="P91" s="2"/>
+      <c r="N91" s="5"/>
+      <c r="O91" s="8"/>
+      <c r="P91" s="8"/>
       <c r="Q91" s="2">
         <v>10</v>
       </c>
@@ -8758,7 +8788,7 @@
         <v>15</v>
       </c>
       <c r="S91" s="2"/>
-      <c r="T91" s="2">
+      <c r="T91" s="11">
         <v>73</v>
       </c>
       <c r="U91" s="2">
@@ -8792,7 +8822,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="92" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="92" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A92" s="2" t="s">
         <v>27</v>
       </c>
@@ -8828,9 +8858,9 @@
       </c>
       <c r="L92" s="2"/>
       <c r="M92" s="2"/>
-      <c r="N92" s="2"/>
-      <c r="O92" s="2"/>
-      <c r="P92" s="2"/>
+      <c r="N92" s="5"/>
+      <c r="O92" s="8"/>
+      <c r="P92" s="8"/>
       <c r="Q92" s="2">
         <v>10</v>
       </c>
@@ -8838,7 +8868,7 @@
         <v>61</v>
       </c>
       <c r="S92" s="2"/>
-      <c r="T92" s="2">
+      <c r="T92" s="11">
         <v>73</v>
       </c>
       <c r="U92" s="2">
@@ -8872,7 +8902,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="93" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="93" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A93" s="2" t="s">
         <v>27</v>
       </c>
@@ -8908,9 +8938,9 @@
       </c>
       <c r="L93" s="2"/>
       <c r="M93" s="2"/>
-      <c r="N93" s="2"/>
-      <c r="O93" s="2"/>
-      <c r="P93" s="2"/>
+      <c r="N93" s="5"/>
+      <c r="O93" s="8"/>
+      <c r="P93" s="8"/>
       <c r="Q93" s="2">
         <v>10</v>
       </c>
@@ -8920,7 +8950,7 @@
       <c r="S93" s="2">
         <v>85</v>
       </c>
-      <c r="T93" s="2">
+      <c r="T93" s="11">
         <v>73</v>
       </c>
       <c r="U93" s="2">
@@ -8954,7 +8984,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="94" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="94" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A94" s="2" t="s">
         <v>27</v>
       </c>
@@ -8990,9 +9020,9 @@
       </c>
       <c r="L94" s="2"/>
       <c r="M94" s="2"/>
-      <c r="N94" s="2"/>
-      <c r="O94" s="2"/>
-      <c r="P94" s="2"/>
+      <c r="N94" s="5"/>
+      <c r="O94" s="8"/>
+      <c r="P94" s="8"/>
       <c r="Q94" s="2">
         <v>10</v>
       </c>
@@ -9002,7 +9032,7 @@
       <c r="S94" s="2">
         <v>46</v>
       </c>
-      <c r="T94" s="2">
+      <c r="T94" s="11">
         <v>73</v>
       </c>
       <c r="U94" s="2">
@@ -9036,7 +9066,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="95" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="95" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A95" s="2" t="s">
         <v>27</v>
       </c>
@@ -9072,9 +9102,9 @@
       </c>
       <c r="L95" s="2"/>
       <c r="M95" s="2"/>
-      <c r="N95" s="2"/>
-      <c r="O95" s="2"/>
-      <c r="P95" s="2"/>
+      <c r="N95" s="5"/>
+      <c r="O95" s="8"/>
+      <c r="P95" s="8"/>
       <c r="Q95" s="2">
         <v>10</v>
       </c>
@@ -9084,7 +9114,7 @@
       <c r="S95" s="2">
         <v>167</v>
       </c>
-      <c r="T95" s="2">
+      <c r="T95" s="11">
         <v>73</v>
       </c>
       <c r="U95" s="2">
@@ -9118,7 +9148,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="96" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="96" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A96" s="2" t="s">
         <v>27</v>
       </c>
@@ -9154,9 +9184,9 @@
       </c>
       <c r="L96" s="2"/>
       <c r="M96" s="2"/>
-      <c r="N96" s="2"/>
-      <c r="O96" s="2"/>
-      <c r="P96" s="2"/>
+      <c r="N96" s="5"/>
+      <c r="O96" s="8"/>
+      <c r="P96" s="8"/>
       <c r="Q96" s="2">
         <v>10</v>
       </c>
@@ -9166,7 +9196,7 @@
       <c r="S96" s="2">
         <v>143</v>
       </c>
-      <c r="T96" s="2">
+      <c r="T96" s="11">
         <v>73</v>
       </c>
       <c r="U96" s="2">
@@ -9200,7 +9230,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="97" spans="1:30" x14ac:dyDescent="0.2">
+    <row r="97" spans="1:30" x14ac:dyDescent="0.25">
       <c r="A97" s="2" t="s">
         <v>27</v>
       </c>
@@ -9236,9 +9266,9 @@
       </c>
       <c r="L97" s="2"/>
       <c r="M97" s="2"/>
-      <c r="N97" s="2"/>
-      <c r="O97" s="2"/>
-      <c r="P97" s="2"/>
+      <c r="N97" s="5"/>
+      <c r="O97" s="8"/>
+      <c r="P97" s="8"/>
       <c r="Q97" s="2">
         <v>10</v>
       </c>
@@ -9248,7 +9278,7 @@
       <c r="S97" s="2">
         <v>239</v>
       </c>
-      <c r="T97" s="2">
+      <c r="T97" s="11">
         <v>73</v>
       </c>
       <c r="U97" s="2">

--- a/raw data/Helen_AcclimationData_stickleback_10and1min.xlsx
+++ b/raw data/Helen_AcclimationData_stickleback_10and1min.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://ljmu-my.sharepoint.com/personal/nspszaji_ljmu_ac_uk/Documents/R &amp; Stats/Acclimation/raw data/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="8" documentId="8_{C88CDE88-DAAA-344E-AC13-A75D1981632C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{DC191757-104A-4EC6-80F0-86876D07FE7F}"/>
+  <xr:revisionPtr revIDLastSave="9" documentId="8_{C88CDE88-DAAA-344E-AC13-A75D1981632C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{F0AF0603-C43D-48FF-A506-C100E6E849F0}"/>
   <bookViews>
-    <workbookView xWindow="37815" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{682BFC1C-55D4-7548-B692-137CFCB24BC9}"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{682BFC1C-55D4-7548-B692-137CFCB24BC9}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -627,18 +627,19 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{25D861FB-907E-174D-BB59-2882214F8FF0}">
   <dimension ref="A1:AD97"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.75" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="15.5" x14ac:dyDescent="0.35"/>
   <cols>
-    <col min="1" max="1" width="17.375" customWidth="1"/>
+    <col min="1" max="1" width="17.33203125" customWidth="1"/>
+    <col min="3" max="3" width="22" customWidth="1"/>
     <col min="12" max="12" width="12" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="12.875" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="14.875" style="6" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="12.83203125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="14.83203125" style="6" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="22.5" style="9" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="11" style="9"/>
     <col min="20" max="20" width="11" style="12"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -730,7 +731,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="2" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A2" s="2" t="s">
         <v>27</v>
       </c>
@@ -822,7 +823,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="3" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A3" s="2" t="s">
         <v>27</v>
       </c>
@@ -914,7 +915,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="4" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A4" s="2" t="s">
         <v>27</v>
       </c>
@@ -1006,7 +1007,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="5" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A5" s="2" t="s">
         <v>27</v>
       </c>
@@ -1098,7 +1099,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="6" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A6" s="2" t="s">
         <v>27</v>
       </c>
@@ -1190,7 +1191,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="7" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A7" s="2" t="s">
         <v>27</v>
       </c>
@@ -1282,7 +1283,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="8" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A8" s="2" t="s">
         <v>27</v>
       </c>
@@ -1374,7 +1375,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A9" s="2" t="s">
         <v>27</v>
       </c>
@@ -1466,7 +1467,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A10" s="2" t="s">
         <v>27</v>
       </c>
@@ -1558,7 +1559,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="11" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A11" s="2" t="s">
         <v>27</v>
       </c>
@@ -1650,7 +1651,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="12" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A12" s="2" t="s">
         <v>27</v>
       </c>
@@ -1742,7 +1743,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="13" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A13" s="2" t="s">
         <v>27</v>
       </c>
@@ -1834,7 +1835,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="14" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A14" s="2" t="s">
         <v>27</v>
       </c>
@@ -1926,7 +1927,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A15" s="2" t="s">
         <v>27</v>
       </c>
@@ -2018,7 +2019,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="16" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A16" s="2" t="s">
         <v>27</v>
       </c>
@@ -2110,7 +2111,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="17" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A17" s="2" t="s">
         <v>27</v>
       </c>
@@ -2202,7 +2203,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="18" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A18" s="2" t="s">
         <v>27</v>
       </c>
@@ -2294,7 +2295,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="19" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A19" s="2" t="s">
         <v>27</v>
       </c>
@@ -2386,7 +2387,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="20" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A20" s="2" t="s">
         <v>27</v>
       </c>
@@ -2478,7 +2479,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="21" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A21" s="2" t="s">
         <v>27</v>
       </c>
@@ -2570,7 +2571,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="22" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A22" s="2" t="s">
         <v>27</v>
       </c>
@@ -2662,7 +2663,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="23" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A23" s="2" t="s">
         <v>27</v>
       </c>
@@ -2754,7 +2755,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="24" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A24" s="2" t="s">
         <v>27</v>
       </c>
@@ -2846,7 +2847,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="25" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A25" s="2" t="s">
         <v>27</v>
       </c>
@@ -2938,7 +2939,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="26" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A26" s="2" t="s">
         <v>27</v>
       </c>
@@ -3030,7 +3031,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="27" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A27" s="2" t="s">
         <v>27</v>
       </c>
@@ -3122,7 +3123,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="28" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A28" s="2" t="s">
         <v>27</v>
       </c>
@@ -3214,7 +3215,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="29" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A29" s="2" t="s">
         <v>27</v>
       </c>
@@ -3306,7 +3307,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="30" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A30" s="2" t="s">
         <v>27</v>
       </c>
@@ -3398,7 +3399,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="31" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A31" s="2" t="s">
         <v>27</v>
       </c>
@@ -3490,7 +3491,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="32" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A32" s="2" t="s">
         <v>27</v>
       </c>
@@ -3582,7 +3583,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="33" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A33" s="2" t="s">
         <v>27</v>
       </c>
@@ -3674,7 +3675,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="34" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A34" s="2" t="s">
         <v>27</v>
       </c>
@@ -3766,7 +3767,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="35" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A35" s="2" t="s">
         <v>27</v>
       </c>
@@ -3858,7 +3859,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="36" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A36" s="2" t="s">
         <v>27</v>
       </c>
@@ -3950,7 +3951,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="37" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A37" s="2" t="s">
         <v>27</v>
       </c>
@@ -4042,7 +4043,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="38" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A38" s="2" t="s">
         <v>27</v>
       </c>
@@ -4134,7 +4135,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="39" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A39" s="2" t="s">
         <v>27</v>
       </c>
@@ -4226,7 +4227,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="40" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A40" s="2" t="s">
         <v>27</v>
       </c>
@@ -4318,7 +4319,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="41" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A41" s="2" t="s">
         <v>27</v>
       </c>
@@ -4410,7 +4411,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="42" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A42" s="2" t="s">
         <v>27</v>
       </c>
@@ -4502,7 +4503,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="43" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A43" s="2" t="s">
         <v>27</v>
       </c>
@@ -4594,7 +4595,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="44" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A44" s="2" t="s">
         <v>27</v>
       </c>
@@ -4686,7 +4687,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="45" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A45" s="2" t="s">
         <v>27</v>
       </c>
@@ -4778,7 +4779,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="46" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A46" s="2" t="s">
         <v>27</v>
       </c>
@@ -4870,7 +4871,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="47" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A47" s="2" t="s">
         <v>27</v>
       </c>
@@ -4962,7 +4963,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="48" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A48" s="2" t="s">
         <v>27</v>
       </c>
@@ -5054,7 +5055,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="49" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A49" s="2" t="s">
         <v>27</v>
       </c>
@@ -5146,7 +5147,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="50" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A50" s="2" t="s">
         <v>27</v>
       </c>
@@ -5238,7 +5239,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="51" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A51" s="2" t="s">
         <v>27</v>
       </c>
@@ -5330,7 +5331,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="52" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A52" s="2" t="s">
         <v>27</v>
       </c>
@@ -5422,7 +5423,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="53" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A53" s="2" t="s">
         <v>27</v>
       </c>
@@ -5514,7 +5515,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="54" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A54" s="2" t="s">
         <v>27</v>
       </c>
@@ -5606,7 +5607,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="55" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A55" s="2" t="s">
         <v>27</v>
       </c>
@@ -5698,7 +5699,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="56" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A56" s="2" t="s">
         <v>27</v>
       </c>
@@ -5790,7 +5791,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="57" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A57" s="2" t="s">
         <v>27</v>
       </c>
@@ -5882,7 +5883,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="58" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A58" s="2" t="s">
         <v>27</v>
       </c>
@@ -5974,7 +5975,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="59" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A59" s="2" t="s">
         <v>27</v>
       </c>
@@ -6066,7 +6067,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="60" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A60" s="2" t="s">
         <v>27</v>
       </c>
@@ -6158,7 +6159,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="61" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A61" s="2" t="s">
         <v>27</v>
       </c>
@@ -6250,7 +6251,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="62" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A62" s="2" t="s">
         <v>27</v>
       </c>
@@ -6342,7 +6343,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="63" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A63" s="2" t="s">
         <v>27</v>
       </c>
@@ -6434,7 +6435,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="64" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A64" s="2" t="s">
         <v>27</v>
       </c>
@@ -6526,7 +6527,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="65" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A65" s="2" t="s">
         <v>27</v>
       </c>
@@ -6618,7 +6619,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="66" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A66" s="2" t="s">
         <v>27</v>
       </c>
@@ -6710,7 +6711,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="67" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A67" s="2" t="s">
         <v>27</v>
       </c>
@@ -6802,7 +6803,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="68" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="68" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A68" s="2" t="s">
         <v>27</v>
       </c>
@@ -6894,7 +6895,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="69" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="69" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A69" s="2" t="s">
         <v>27</v>
       </c>
@@ -6986,7 +6987,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="70" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="70" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A70" s="2" t="s">
         <v>27</v>
       </c>
@@ -7078,7 +7079,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="71" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="71" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A71" s="2" t="s">
         <v>27</v>
       </c>
@@ -7170,7 +7171,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="72" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="72" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A72" s="2" t="s">
         <v>27</v>
       </c>
@@ -7262,7 +7263,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="73" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="73" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A73" s="2" t="s">
         <v>27</v>
       </c>
@@ -7354,7 +7355,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="74" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="74" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A74" s="2" t="s">
         <v>27</v>
       </c>
@@ -7436,7 +7437,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="75" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="75" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A75" s="2" t="s">
         <v>27</v>
       </c>
@@ -7516,7 +7517,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="76" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="76" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A76" s="2" t="s">
         <v>27</v>
       </c>
@@ -7598,7 +7599,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="77" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="77" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A77" s="2" t="s">
         <v>27</v>
       </c>
@@ -7680,7 +7681,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="78" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="78" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A78" s="2" t="s">
         <v>27</v>
       </c>
@@ -7762,7 +7763,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="79" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="79" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A79" s="2" t="s">
         <v>27</v>
       </c>
@@ -7842,7 +7843,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="80" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="80" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A80" s="2" t="s">
         <v>27</v>
       </c>
@@ -7924,7 +7925,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="81" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="81" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A81" s="2" t="s">
         <v>27</v>
       </c>
@@ -8006,7 +8007,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="82" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="82" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A82" s="2" t="s">
         <v>27</v>
       </c>
@@ -8088,7 +8089,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="83" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="83" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A83" s="2" t="s">
         <v>27</v>
       </c>
@@ -8170,7 +8171,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="84" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="84" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A84" s="2" t="s">
         <v>27</v>
       </c>
@@ -8252,7 +8253,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="85" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="85" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A85" s="2" t="s">
         <v>27</v>
       </c>
@@ -8334,7 +8335,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="86" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="86" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A86" s="2" t="s">
         <v>27</v>
       </c>
@@ -8414,7 +8415,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="87" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="87" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A87" s="2" t="s">
         <v>27</v>
       </c>
@@ -8496,7 +8497,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="88" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="88" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A88" s="2" t="s">
         <v>27</v>
       </c>
@@ -8578,7 +8579,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="89" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="89" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A89" s="2" t="s">
         <v>27</v>
       </c>
@@ -8660,7 +8661,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="90" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="90" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A90" s="2" t="s">
         <v>27</v>
       </c>
@@ -8742,7 +8743,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="91" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="91" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A91" s="2" t="s">
         <v>27</v>
       </c>
@@ -8822,7 +8823,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="92" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="92" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A92" s="2" t="s">
         <v>27</v>
       </c>
@@ -8902,7 +8903,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="93" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="93" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A93" s="2" t="s">
         <v>27</v>
       </c>
@@ -8984,7 +8985,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="94" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="94" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A94" s="2" t="s">
         <v>27</v>
       </c>
@@ -9066,7 +9067,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="95" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="95" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A95" s="2" t="s">
         <v>27</v>
       </c>
@@ -9148,7 +9149,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="96" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="96" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A96" s="2" t="s">
         <v>27</v>
       </c>
@@ -9230,7 +9231,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="97" spans="1:30" x14ac:dyDescent="0.25">
+    <row r="97" spans="1:30" x14ac:dyDescent="0.35">
       <c r="A97" s="2" t="s">
         <v>27</v>
       </c>
